--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -132,8 +132,7 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
     <font>
@@ -179,7 +178,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -330,7 +330,7 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -354,7 +354,7 @@
     <xf numFmtId="0" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -854,7 +854,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -920,7 +920,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -6485,7 +6485,7 @@
           <t>A | 1170呎 (3房)
 $4380万
 $37,440/呎
-(25年-03月-10日)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -6493,7 +6493,7 @@
           <t>B | 1171呎 (3房)
 $4380万
 $37,404/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
           <t>B | 2511呎 (4+房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
           <t>A | 1100呎 (3房)
 $2911万
 $26,464/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -6539,7 +6539,7 @@
           <t>B | 1097呎 (3房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -6665,7 +6665,7 @@
           <t>A | 1170呎 (3房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -6673,7 +6673,7 @@
           <t>B | 1215呎 (3房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
           <t>B | 1097呎 (3房)
 $2768万
 $25,232/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
     </row>
@@ -6795,12 +6795,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -6859,7 +6859,7 @@
           <t>C | 2452呎 (4+房)
 $8776万
 $35,791/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -6867,7 +6867,7 @@
           <t>D | 2437呎 (4+房)
 $8223万
 $33,743/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
           <t>A | 2436呎 (4+房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -6890,7 +6890,7 @@
           <t>B | 2436呎 (4+房)
 $8778万
 $36,034/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -6970,12 +6970,12 @@
       </c>
       <c r="B3" s="26" t="inlineStr">
         <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
           <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>2 套</t>
         </is>
       </c>
       <c r="D3" s="28" t="inlineStr">
@@ -7050,7 +7050,7 @@
         <is>
           <t>2号屋
 4706呎 (4+房)
-(26年-07月-06日)
+(26年-07月-07日)
 $2.68亿
 $56,949/呎</t>
         </is>
@@ -7059,8 +7059,8 @@
         <is>
           <t>3号屋
 4662呎 (4+房)
-(已定价未售)
-招标单位
+(在售)
+招标项目
 -</t>
         </is>
       </c>
@@ -7068,7 +7068,7 @@
         <is>
           <t>5号屋
 4666呎 (4+房)
-(26年-02月-09日)
+(26年-02月-10日)
 $2.47亿
 $52,846/呎</t>
         </is>
@@ -7120,7 +7120,7 @@
         <is>
           <t>10号屋
 5239呎 (4+房)
-(25年-12月-23日)
+(25年-12月-24日)
 $3.23亿
 $61,596/呎</t>
         </is>
@@ -7129,7 +7129,7 @@
         <is>
           <t>11号屋
 3336呎 (4+房)
-(26年-07月-19日)
+(26年-07月-20日)
 $1.51亿
 $45,288/呎</t>
         </is>
@@ -7138,8 +7138,8 @@
         <is>
           <t>12号屋
 2716呎 (4+房)
-(在售)
-招标项目
+(已定价未售)
+招标单位
 -</t>
         </is>
       </c>
@@ -7147,8 +7147,8 @@
         <is>
           <t>15号屋
 2695呎 (4+房)
-(在售)
-招标项目
+(已定价未售)
+招标单位
 -</t>
         </is>
       </c>
@@ -7163,7 +7163,7 @@
         <is>
           <t>16号屋
 3053呎 (4+房)
-(26年-07月-12日)
+(26年-07月-13日)
 $1.17亿
 $38,257/呎</t>
         </is>
@@ -7172,8 +7172,8 @@
         <is>
           <t>17号屋
 3059呎 (4+房)
-(在售)
-招标项目
+(已定价未售)
+招标单位
 -</t>
         </is>
       </c>
@@ -7181,7 +7181,7 @@
         <is>
           <t>18号屋
 5509呎 (4+房)
-(25年-12月-23日)
+(25年-12月-24日)
 $3.62亿
 $65,801/呎</t>
         </is>
@@ -7199,7 +7199,7 @@
         <is>
           <t>20号屋
 3436呎 (4+房)
-(25年-07月-22日)
+(25年-07月-23日)
 $1.38亿
 $40,163/呎</t>
         </is>
@@ -7208,7 +7208,7 @@
         <is>
           <t>21号屋
 3297呎 (4+房)
-(26年-04月-22日)
+(26年-04月-23日)
 $1.39亿
 $42,069/呎</t>
         </is>
@@ -7224,7 +7224,7 @@
         <is>
           <t>22号屋
 3285呎 (4+房)
-(25年-10月-05日)
+(25年-10月-06日)
 $1.38亿
 $42,009/呎</t>
         </is>
@@ -7233,7 +7233,7 @@
         <is>
           <t>23号屋
 3272呎 (4+房)
-(25年-09月-03日)
+(25年-09月-04日)
 $1.40亿
 $42,784/呎</t>
         </is>
@@ -7242,7 +7242,7 @@
         <is>
           <t>25号屋
 3289呎 (4+房)
-(26年-06月-25日)
+(26年-07月-27日)
 $1.63亿
 $49,504/呎</t>
         </is>
@@ -7260,7 +7260,7 @@
         <is>
           <t>27号屋
 3304呎 (4+房)
-(24年-06月-24日)
+(24年-06月-25日)
 $1.46亿
 $44,200/呎</t>
         </is>
@@ -7269,7 +7269,7 @@
         <is>
           <t>28号屋
 5260呎 (4+房)
-(25年-04月-07日)
+(25年-04月-08日)
 $2.60亿
 $49,495/呎</t>
         </is>
@@ -7294,7 +7294,7 @@
         <is>
           <t>30号屋
 2738呎 (4+房)
-(26年-02月-12日)
+(26年-02月-13日)
 $1.07亿
 $39,248/呎</t>
         </is>
@@ -7303,7 +7303,7 @@
         <is>
           <t>31号屋
 2739呎 (4+房)
-(24年-11月-28日)
+(24年-11月-29日)
 $9,614万
 $35,099/呎</t>
         </is>
@@ -7311,51 +7311,51 @@
       <c r="E10" s="22" t="inlineStr">
         <is>
           <t>32号屋
+3063呎 (4+房)
+(已定价未售)
+招标单位
+-</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>33号屋
+3102呎 (4+房)
+(24年-05月-30日)
+$1.15亿
+$37,150/呎</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>35号屋
+3102呎 (4+房)
+(24年-05月-14日)
+$1.16亿
+$37,344/呎</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>36号屋
 3063呎 (4+房)
 (在售)
 招标项目
 -</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>33号屋
-3102呎 (4+房)
-(24年-05月-29日)
-$1.15亿
-$37,150/呎</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>35号屋
-3102呎 (4+房)
-(24年-05月-13日)
-$1.16亿
-$37,344/呎</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>36号屋
-3063呎 (4+房)
-(已定价未售)
-招标单位
--</t>
-        </is>
-      </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
           <t>38号屋
 4692呎 (4+房)
-(25年-11月-06日)
+(25年-11月-07日)
 $2.56亿
 $54,561/呎</t>
         </is>
@@ -7501,7 +7501,7 @@
           <t>C | 2452呎 (4+房)
 $8620万
 $35,155/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -7509,7 +7509,7 @@
           <t>D | 2551呎 (4+房)
 $8307万
 $32,564/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
           <t>A | 2466呎 (4+房)
 $17361万
 $70,403/呎
-(24年-04月-29日)</t>
+(24年-04月-30日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -7532,7 +7532,7 @@
           <t>B | 2466呎 (4+房)
 $17361万
 $70,403/呎
-(24年-04月-29日)</t>
+(24年-04月-30日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -7610,12 +7610,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -7674,7 +7674,7 @@
           <t>C | 2566呎 (4+房)
 $9469万
 $36,900/呎
-(24年-08月-04日)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -7682,7 +7682,7 @@
           <t>D | 2437呎 (4+房)
 $8502万
 $34,887/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
           <t>A | 2466呎 (4+房)
 $8412万
 $34,111/呎
-(24年-05月-09日)</t>
+(24年-05月-10日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -7705,7 +7705,7 @@
           <t>B | 2436呎 (4+房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -7834,7 +7834,7 @@
           <t>B | 3212呎 (4+房)
 $11980万
 $37,298/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
           <t>A | 3198呎 (4+房)
 $12776万
 $39,950/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr"/>
@@ -7976,7 +7976,7 @@
           <t>A | 1931呎 (4+房)
 $6373万
 $33,002/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -7984,7 +7984,7 @@
           <t>B | 1851呎 (4+房)
 $7337万
 $39,638/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
           <t>A | 1826呎 (4+房)
 $5387万
 $29,502/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -8007,7 +8007,7 @@
           <t>B | 1805呎 (4+房)
 $5315万
 $29,446/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
           <t>A | 1931呎 (4+房)
 $6083万
 $31,502/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -8141,7 +8141,7 @@
           <t>B | 1851呎 (4+房)
 $6109万
 $33,003/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8156,7 @@
           <t>A | 1826呎 (4+房)
 $5254万
 $28,773/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -8164,7 +8164,7 @@
           <t>B | 1805呎 (4+房)
 $5533万
 $30,654/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -8290,7 +8290,7 @@
           <t>A | 1871呎 (4+房)
 $6752万
 $36,086/呎
-(24年-11月-13日)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr"/>
@@ -8314,7 +8314,7 @@
           <t>B | 1855呎 (4+房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -8411,12 +8411,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -8464,7 +8464,7 @@
           <t>B | 1871呎 (4+房)
 $7708万
 $41,197/呎
-(25年-02月-17日)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
           <t>A | 844呎 (2房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -8510,7 +8510,7 @@
           <t>B | 834呎 (2房)
 $2450万
 $29,376/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
           <t>A | 1170呎 (3房)
 $4380万
 $37,440/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -8644,7 +8644,7 @@
           <t>B | 1171呎 (3房)
 $4382万
 $37,421/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -8667,7 +8667,7 @@
           <t>B | 2511呎 (4+房)
 $6812万
 $27,129/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
           <t>A | 1100呎 (3房)
 $2860万
 $26,000/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -8690,7 +8690,7 @@
           <t>B | 1097呎 (3房)
 $3159万
 $28,801/呎
-(25年-03月-05日)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,7 +132,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -175,12 +176,6 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
     </font>
   </fonts>
   <fills count="10">
@@ -265,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -330,7 +325,7 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -353,9 +348,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1245,7 +1237,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2107,7 +2099,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2659,7 +2651,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3261,7 +3253,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3401,7 +3393,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3537,7 +3529,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3607,7 +3599,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -4151,7 +4143,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -4905,7 +4897,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4975,7 +4967,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -5111,7 +5103,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -6051,7 +6043,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -6433,12 +6425,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -6516,7 +6508,7 @@
           <t>B | 2511呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6531,7 @@
           <t>B | 1097呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6605,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -6665,7 +6657,7 @@
           <t>A | 1170呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -6673,7 +6665,7 @@
           <t>B | 1215呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -6795,12 +6787,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -6882,7 +6874,7 @@
           <t>A | 2436呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -6970,12 +6962,12 @@
       </c>
       <c r="B3" s="26" t="inlineStr">
         <is>
-          <t>2 套</t>
+          <t>6 套</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>4 套</t>
+          <t>0 套</t>
         </is>
       </c>
       <c r="D3" s="28" t="inlineStr">
@@ -7055,7 +7047,7 @@
 $56,949/呎</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>3号屋
 4662呎 (4+房)
@@ -7138,8 +7130,8 @@
         <is>
           <t>12号屋
 2716呎 (4+房)
-(已定价未售)
-招标单位
+(在售)
+招标项目
 -</t>
         </is>
       </c>
@@ -7147,8 +7139,8 @@
         <is>
           <t>15号屋
 2695呎 (4+房)
-(已定价未售)
-招标单位
+(在售)
+招标项目
 -</t>
         </is>
       </c>
@@ -7172,8 +7164,8 @@
         <is>
           <t>17号屋
 3059呎 (4+房)
-(已定价未售)
-招标单位
+(在售)
+招标项目
 -</t>
         </is>
       </c>
@@ -7312,8 +7304,8 @@
         <is>
           <t>32号屋
 3063呎 (4+房)
-(已定价未售)
-招标单位
+(在售)
+招标项目
 -</t>
         </is>
       </c>
@@ -7342,7 +7334,7 @@
           <t>第 6 行</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>36号屋
 3063呎 (4+房)
@@ -7360,10 +7352,10 @@
 $54,561/呎</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr"/>
-      <c r="E11" s="31" t="inlineStr"/>
-      <c r="F11" s="31" t="inlineStr"/>
-      <c r="G11" s="31" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr"/>
+      <c r="E11" s="30" t="inlineStr"/>
+      <c r="F11" s="30" t="inlineStr"/>
+      <c r="G11" s="30" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7610,12 +7602,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -7705,7 +7697,7 @@
           <t>B | 2436呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -8238,12 +8230,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -8314,7 +8306,7 @@
           <t>B | 1855呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -8411,12 +8403,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -8502,7 +8494,7 @@
           <t>A | 844呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">

--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -177,6 +177,11 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -260,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -348,6 +353,9 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4827,7 +4835,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>3336</v>
+        <v>3297</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4836,14 +4844,14 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
         <v>151080000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>45288</v>
+        <v>45823</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -5841,7 +5849,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -5851,12 +5859,12 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -5866,12 +5874,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -5881,7 +5889,7 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6967,22 +6975,22 @@
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>18 套</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
-        <is>
-          <t>18 套</t>
-        </is>
-      </c>
-      <c r="E3" s="29" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>8 套</t>
+          <t>7 套</t>
         </is>
       </c>
     </row>
@@ -7120,10 +7128,10 @@
       <c r="E7" s="21" t="inlineStr">
         <is>
           <t>11号屋
-3336呎 (4+房)
-(26年-07月-20日)
+3297呎 (4+房)
+(26年-08月-07日)
 $1.51亿
-$45,288/呎</t>
+$45,823/呎</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -7273,13 +7281,13 @@
           <t>第 5 行</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>29号屋
 3382呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
+(已定价未售)
+招标单位
+-</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -7352,10 +7360,10 @@
 $54,561/呎</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr"/>
-      <c r="E11" s="30" t="inlineStr"/>
-      <c r="F11" s="30" t="inlineStr"/>
-      <c r="G11" s="30" t="inlineStr"/>
+      <c r="D11" s="31" t="inlineStr"/>
+      <c r="E11" s="31" t="inlineStr"/>
+      <c r="F11" s="31" t="inlineStr"/>
+      <c r="G11" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -5849,7 +5849,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -6994,6 +6994,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -7281,11 +7282,11 @@
           <t>第 5 行</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>29号屋
 3382呎 (4+房)
-(已定价未售)
+(在售)
 招标单位
 -</t>
         </is>

--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -8,18 +8,18 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12座" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6389,7 +6389,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>7座 销控网格图</t>
+          <t>6座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6485,15 +6485,15 @@
           <t>A | 1170呎 (3房)
 $4380万
 $37,440/呎
-(25年-03月-11日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 1171呎 (3房)
-$4380万
-$37,404/呎
-(25年-05月-15日)</t>
+$4382万
+$37,421/呎
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -6511,12 +6511,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 2511呎 (4+房)
-招标单位
--
-(在售)</t>
+$6812万
+$27,129/呎
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -6529,17 +6529,17 @@
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 1100呎 (3房)
-$2911万
-$26,464/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
+$2860万
+$26,000/呎
+(25年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1097呎 (3房)
-招标单位
--
-(在售)</t>
+$3159万
+$28,801/呎
+(25年-03月-06日)</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>8座 销控网格图</t>
+          <t>7座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -6623,17 +6623,17 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
     </row>
@@ -6660,66 +6660,66 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>A | 1170呎 (3房)
+$4380万
+$37,440/呎
+(25年-03月-11日)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (3房)
+$4380万
+$37,404/呎
+(25年-05月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 2511呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>B | 1215呎 (3房)
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1100呎 (3房)
+$2911万
+$26,464/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1097呎 (3房)
 招标单位
 -
 (在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>1&amp;2</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>A | 2456呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>B | 2565呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 1100呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1097呎 (3房)
-$2768万
-$25,232/呎
-(26年-02月-24日)</t>
         </is>
       </c>
     </row>
@@ -6733,6 +6733,186 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>8座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 1170呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 1215呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 2456呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 2565呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 1100呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1097呎 (3房)
+$2768万
+$25,232/呎
+(26年-02月-24日)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6905,7 +7085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6994,7 +7174,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -7369,179 +7548,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>10座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>2&amp;3</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>C | 2452呎 (4+房)
-$8620万
-$35,155/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 2551呎 (4+房)
-$8307万
-$32,564/呎
-(24年-05月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 2466呎 (4+房)
-$17361万
-$70,403/呎
-(24年-04月-30日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 2466呎 (4+房)
-$17361万
-$70,403/呎
-(24年-04月-30日)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -7567,7 +7573,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>11座 销控网格图</t>
+          <t>10座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -7611,7 +7617,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7621,7 +7627,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7672,18 +7678,18 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 2566呎 (4+房)
-$9469万
-$36,900/呎
-(24年-08月-05日)</t>
+          <t>C | 2452呎 (4+房)
+$8620万
+$35,155/呎
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 2437呎 (4+房)
-$8502万
-$34,887/呎
-(26年-05月-11日)</t>
+          <t>D | 2551呎 (4+房)
+$8307万
+$32,564/呎
+(24年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -7696,17 +7702,17 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 2466呎 (4+房)
-$8412万
-$34,111/呎
-(24年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>B | 2436呎 (4+房)
-招标单位
--
-(在售)</t>
+$17361万
+$70,403/呎
+(24年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2466呎 (4+房)
+$17361万
+$70,403/呎
+(24年-04月-30日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -7733,12 +7739,14 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>12座 销控网格图</t>
+          <t>11座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -7777,22 +7785,22 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7822,6 +7830,16 @@
           <t>B</t>
         </is>
       </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -7830,12 +7848,21 @@
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 3212呎 (4+房)
-$11980万
-$37,298/呎
-(26年-06月-08日)</t>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 2566呎 (4+房)
+$9469万
+$36,900/呎
+(24年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 2437呎 (4+房)
+$8502万
+$34,887/呎
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -7847,13 +7874,22 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 3198呎 (4+房)
-$12776万
-$39,950/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
+          <t>A | 2466呎 (4+房)
+$8412万
+$34,111/呎
+(24年-05月-10日)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 2436呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7881,7 +7917,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>1座 销控网格图</t>
+          <t>12座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7956,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
@@ -7935,7 +7971,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7972,20 +8008,13 @@
           <t>2&amp;3</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>A | 1931呎 (4+房)
-$6373万
-$33,002/呎
-(24年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1851呎 (4+房)
-$7337万
-$39,638/呎
-(26年-06月-03日)</t>
+          <t>B | 3212呎 (4+房)
+$11980万
+$37,298/呎
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -7997,20 +8026,13 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 1826呎 (4+房)
-$5387万
-$29,502/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 1805呎 (4+房)
-$5315万
-$29,446/呎
-(24年-05月-14日)</t>
-        </is>
-      </c>
+          <t>A | 3198呎 (4+房)
+$12776万
+$39,950/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8038,7 +8060,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>2座 销控网格图</t>
+          <t>1座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -8132,17 +8154,17 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t>A | 1931呎 (4+房)
-$6083万
-$31,502/呎
-(24年-05月-14日)</t>
+$6373万
+$33,002/呎
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 1851呎 (4+房)
-$6109万
-$33,003/呎
-(24年-05月-20日)</t>
+$7337万
+$39,638/呎
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -8155,17 +8177,17 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 1826呎 (4+房)
-$5254万
-$28,773/呎
-(25年-02月-06日)</t>
+$5387万
+$29,502/呎
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1805呎 (4+房)
-$5533万
-$30,654/呎
-(25年-11月-25日)</t>
+$5315万
+$29,446/呎
+(24年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8195,7 +8217,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>3座 销控网格图</t>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -8234,12 +8256,12 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -8249,17 +8271,17 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8283,62 +8305,46 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2&amp;3</t>
         </is>
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1871呎 (4+房)
-$6752万
-$36,086/呎
-(24年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr"/>
+          <t>A | 1931呎 (4+房)
+$6083万
+$31,502/呎
+(24年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 1851呎 (4+房)
+$6109万
+$33,003/呎
+(24年-05月-20日)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>1&amp;2</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>A | 1874呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>B | 1855呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>A | 844呎 (2房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>B | 834呎 (2房)
--
--
-(待售)</t>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 1826呎 (4+房)
+$5254万
+$28,773/呎
+(25年-02月-06日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1805呎 (4+房)
+$5533万
+$30,654/呎
+(25年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8374,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>5座 销控网格图</t>
+          <t>3座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -8422,12 +8428,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -8459,15 +8465,15 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 1871呎 (4+房)
-$7708万
-$41,197/呎
-(25年-02月-18日)</t>
-        </is>
-      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1871呎 (4+房)
+$6752万
+$36,086/呎
+(24年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -8477,41 +8483,41 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 1931呎 (4+房)
+          <t>A | 1874呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>B | 1910呎 (4+房)
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1855呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>A | 844呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 834呎 (2房)
 -
 -
 (待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 844呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 834呎 (2房)
-$2450万
-$29,376/呎
-(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8547,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>6座 销控网格图</t>
+          <t>5座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -8580,32 +8586,32 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -8632,20 +8638,13 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>A | 1170呎 (3房)
-$4380万
-$37,440/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
+      <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1171呎 (3房)
-$4382万
-$37,421/呎
-(26年-05月-11日)</t>
+          <t>B | 1871呎 (4+房)
+$7708万
+$41,197/呎
+(25年-02月-18日)</t>
         </is>
       </c>
     </row>
@@ -8657,18 +8656,18 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 2403呎 (4+房)
+          <t>A | 1931呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 2511呎 (4+房)
-$6812万
-$27,129/呎
-(26年-05月-11日)</t>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 1910呎 (4+房)
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -8678,20 +8677,20 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 1100呎 (3房)
-$2860万
-$26,000/呎
-(25年-04月-23日)</t>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 844呎 (2房)
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>B | 1097呎 (3房)
-$3159万
-$28,801/呎
-(25年-03月-06日)</t>
+          <t>B | 834呎 (2房)
+$2450万
+$29,376/呎
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -8,18 +8,18 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11座" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12座" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -144,12 +144,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
     </font>
@@ -176,11 +170,6 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
     </font>
   </fonts>
   <fills count="10">
@@ -265,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -336,26 +325,20 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2247,7 +2230,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2257,12 +2240,12 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2272,12 +2255,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2287,7 +2270,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2300,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2327,12 +2310,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2342,12 +2325,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2357,7 +2340,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3537,23 +3520,19 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>42750000</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>35185</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3562,12 +3541,12 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -3577,7 +3556,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4151,23 +4130,19 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>86950000</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>35694</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4176,12 +4151,12 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -4191,7 +4166,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5111,23 +5086,19 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>118070000</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>38598</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -5136,12 +5107,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -5151,7 +5122,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6360,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>6座 销控网格图</t>
+          <t>7座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -6433,17 +6404,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6485,15 +6456,15 @@
           <t>A | 1170呎 (3房)
 $4380万
 $37,440/呎
-(25年-07月-22日)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 1171呎 (3房)
-$4382万
-$37,421/呎
-(26年-05月-11日)</t>
+$4380万
+$37,404/呎
+(25年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -6511,12 +6482,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 2511呎 (4+房)
-$6812万
-$27,129/呎
-(26年-05月-11日)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -6529,17 +6500,17 @@
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 1100呎 (3房)
-$2860万
-$26,000/呎
-(25年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
+$2911万
+$26,464/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1097呎 (3房)
-$3159万
-$28,801/呎
-(25年-03月-06日)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6540,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>7座 销控网格图</t>
+          <t>8座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -6613,27 +6584,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6631,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 1170呎 (3房)
-$4380万
-$37,440/呎
-(25年-03月-11日)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1171呎 (3房)
-$4380万
-$37,404/呎
-(25年-05月-15日)</t>
+          <t>B | 1215呎 (3房)
+$4275万
+$35,185/呎
+(26年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -6685,18 +6656,18 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 2403呎 (4+房)
+          <t>A | 2456呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>B | 2511呎 (4+房)
-招标单位
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 2565呎 (4+房)
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6677,20 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1100呎 (3房)
-$2911万
-$26,464/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1097呎 (3房)
-招标单位
--
-(在售)</t>
+$2768万
+$25,232/呎
+(26年-02月-24日)</t>
         </is>
       </c>
     </row>
@@ -6733,186 +6704,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>8座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>A | 1170呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>B | 1215呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>1&amp;2</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>A | 2456呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>B | 2565呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 1100呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1097呎 (3房)
-$2768万
-$25,232/呎
-(26年-02月-24日)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6975,7 +6766,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6985,7 +6776,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7057,12 +6848,12 @@
           <t>G&amp;1</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 2436呎 (4+房)
-招标单位
--
-(在售)</t>
+$8695万
+$35,694/呎
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -7085,7 +6876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7143,32 +6934,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>32 套</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>6 套</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="D3" s="28" t="inlineStr">
-        <is>
-          <t>18 套</t>
-        </is>
-      </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="25" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
+        <is>
+          <t>19 套</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>7 套</t>
         </is>
@@ -7348,13 +7139,13 @@
 $38,257/呎</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>17号屋
 3059呎 (4+房)
-(在售)
-招标项目
--</t>
+(26年-08月-12日)
+$1.18亿
+$38,598/呎</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -7466,7 +7257,7 @@
           <t>29号屋
 3382呎 (4+房)
 (在售)
-招标单位
+招标项目
 -</t>
         </is>
       </c>
@@ -7540,14 +7331,187 @@
 $54,561/呎</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr"/>
-      <c r="E11" s="31" t="inlineStr"/>
-      <c r="F11" s="31" t="inlineStr"/>
-      <c r="G11" s="31" t="inlineStr"/>
+      <c r="D11" s="29" t="inlineStr"/>
+      <c r="E11" s="29" t="inlineStr"/>
+      <c r="F11" s="29" t="inlineStr"/>
+      <c r="G11" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>10座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 2452呎 (4+房)
+$8620万
+$35,155/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 2551呎 (4+房)
+$8307万
+$32,564/呎
+(24年-05月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2466呎 (4+房)
+$17361万
+$70,403/呎
+(24年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2466呎 (4+房)
+$17361万
+$70,403/呎
+(24年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -7573,7 +7537,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>10座 销控网格图</t>
+          <t>11座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -7617,17 +7581,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7678,18 +7642,18 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 2452呎 (4+房)
-$8620万
-$35,155/呎
-(26年-07月-07日)</t>
+          <t>C | 2566呎 (4+房)
+$9469万
+$36,900/呎
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 2551呎 (4+房)
-$8307万
-$32,564/呎
-(24年-05月-24日)</t>
+          <t>D | 2437呎 (4+房)
+$8502万
+$34,887/呎
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -7702,17 +7666,17 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 2466呎 (4+房)
-$17361万
-$70,403/呎
-(24年-04月-30日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 2466呎 (4+房)
-$17361万
-$70,403/呎
-(24年-04月-30日)</t>
+$8412万
+$34,111/呎
+(24年-05月-10日)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 2436呎 (4+房)
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -7739,14 +7703,12 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>11座 销控网格图</t>
+          <t>12座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7747,12 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7800,7 +7762,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7830,16 +7792,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -7848,21 +7800,12 @@
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>C | 2566呎 (4+房)
-$9469万
-$36,900/呎
-(24年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 2437呎 (4+房)
-$8502万
-$34,887/呎
-(26年-05月-11日)</t>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 3212呎 (4+房)
+$11980万
+$37,298/呎
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -7874,22 +7817,13 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 2466呎 (4+房)
-$8412万
-$34,111/呎
-(24年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>B | 2436呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
+          <t>A | 3198呎 (4+房)
+$12776万
+$39,950/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7917,7 +7851,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>12座 销控网格图</t>
+          <t>1座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7890,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
@@ -7971,7 +7905,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8008,13 +7942,20 @@
           <t>2&amp;3</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1931呎 (4+房)
+$6373万
+$33,002/呎
+(24年-05月-17日)</t>
+        </is>
+      </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 3212呎 (4+房)
-$11980万
-$37,298/呎
-(26年-06月-08日)</t>
+          <t>B | 1851呎 (4+房)
+$7337万
+$39,638/呎
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -8026,13 +7967,20 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 3198呎 (4+房)
-$12776万
-$39,950/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
+          <t>A | 1826呎 (4+房)
+$5387万
+$29,502/呎
+(26年-03月-25日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1805呎 (4+房)
+$5315万
+$29,446/呎
+(24年-05月-14日)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8060,7 +8008,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>1座 销控网格图</t>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -8154,17 +8102,17 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t>A | 1931呎 (4+房)
-$6373万
-$33,002/呎
-(24年-05月-17日)</t>
+$6083万
+$31,502/呎
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 1851呎 (4+房)
-$7337万
-$39,638/呎
-(26年-06月-03日)</t>
+$6109万
+$33,003/呎
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -8177,17 +8125,17 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 1826呎 (4+房)
-$5387万
-$29,502/呎
-(26年-03月-25日)</t>
+$5254万
+$28,773/呎
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1805呎 (4+房)
-$5315万
-$29,446/呎
-(24年-05月-14日)</t>
+$5533万
+$30,654/呎
+(25年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8217,7 +8165,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>2座 销控网格图</t>
+          <t>3座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -8256,32 +8204,32 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8305,46 +8253,62 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>2&amp;3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1931呎 (4+房)
-$6083万
-$31,502/呎
-(24年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 1851呎 (4+房)
-$6109万
-$33,003/呎
-(24年-05月-20日)</t>
-        </is>
-      </c>
+          <t>A | 1871呎 (4+房)
+$6752万
+$36,086/呎
+(24年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 1826呎 (4+房)
-$5254万
-$28,773/呎
-(25年-02月-06日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 1805呎 (4+房)
-$5533万
-$30,654/呎
-(25年-11月-25日)</t>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1874呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1855呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 844呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 834呎 (2房)
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8338,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>3座 销控网格图</t>
+          <t>5座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -8428,12 +8392,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -8465,15 +8429,15 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>A | 1871呎 (4+房)
-$6752万
-$36,086/呎
-(24年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr"/>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 1871呎 (4+房)
+$7708万
+$41,197/呎
+(25年-02月-18日)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -8483,41 +8447,41 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 1874呎 (4+房)
+          <t>A | 1931呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>B | 1855呎 (4+房)
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 1910呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 844呎 (2房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>A | 844呎 (2房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 834呎 (2房)
--
--
-(待售)</t>
+$2450万
+$29,376/呎
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>5座 销控网格图</t>
+          <t>6座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -8586,32 +8550,32 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
     </row>
@@ -8638,13 +8602,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1170呎 (3房)
+$4380万
+$37,440/呎
+(25年-07月-22日)</t>
+        </is>
+      </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1871呎 (4+房)
-$7708万
-$41,197/呎
-(25年-02月-18日)</t>
+          <t>B | 1171呎 (3房)
+$4382万
+$37,421/呎
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -8656,18 +8627,18 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 1931呎 (4+房)
+          <t>A | 2403呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>B | 1910呎 (4+房)
--
--
-(待售)</t>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2511呎 (4+房)
+$6812万
+$27,129/呎
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -8677,20 +8648,20 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 844呎 (2房)
-招标单位
--
-(在售)</t>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1100呎 (3房)
+$2860万
+$26,000/呎
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>B | 834呎 (2房)
-$2450万
-$29,376/呎
-(25年-03月-20日)</t>
+          <t>B | 1097呎 (3房)
+$3159万
+$28,801/呎
+(25年-03月-06日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -2230,23 +2230,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>23420000</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>28082</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2255,12 +2251,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2270,7 +2266,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2300,23 +2296,19 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>23980000</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>28412</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2325,12 +2317,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2340,7 +2332,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8209,17 +8201,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8295,20 +8287,20 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 844呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
+$2398万
+$28,412/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 834呎 (2房)
-招标单位
--
-(在售)</t>
+$2342万
+$28,082/呎
+(26年-08月-17日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -3718,7 +3718,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6576,27 +6576,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 2456呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -6669,12 +6669,12 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1100呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">

--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -4324,23 +4324,19 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>249160000</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>53445</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4349,12 +4345,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4364,7 +4360,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6929,7 @@
       </c>
       <c r="B3" s="25" t="inlineStr">
         <is>
-          <t>6 套</t>
+          <t>5 套</t>
         </is>
       </c>
       <c r="C3" s="26" t="inlineStr">
@@ -6943,7 +6939,7 @@
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
-          <t>19 套</t>
+          <t>20 套</t>
         </is>
       </c>
       <c r="E3" s="28" t="inlineStr">
@@ -7018,13 +7014,13 @@
 $56,949/呎</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>3号屋
 4662呎 (4+房)
-(在售)
-招标项目
--</t>
+(26年-08月-26日)
+$2.49亿
+$53,445/呎</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">

--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -132,13 +132,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -319,10 +319,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1228,23 +1228,19 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>84680000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>34762</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1253,12 +1249,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1268,7 +1264,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6458,7 @@
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 2403呎 (4+房)
 -
@@ -6470,7 +6466,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 2511呎 (4+房)
 招标单位
@@ -6493,7 +6489,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 1097呎 (3房)
 招标单位
@@ -6619,7 +6615,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>A | 1170呎 (3房)
 招标单位
@@ -6642,7 +6638,7 @@
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 2456呎 (4+房)
 招标单位
@@ -6650,7 +6646,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 2565呎 (4+房)
 -
@@ -6665,7 +6661,7 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1100呎 (3房)
 招标单位
@@ -6996,7 +6992,7 @@
           <t>第 1 行</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>1号屋
 7079呎 (3房)
@@ -7032,7 +7028,7 @@
 $52,846/呎</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>6号屋
 4737呎 (4+房)
@@ -7041,7 +7037,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>7号屋
 4728呎 (4+房)
@@ -7057,7 +7053,7 @@
           <t>第 2 行</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>8号屋
 6723呎 (4+房)
@@ -7066,7 +7062,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>9号屋
 3601呎 (4+房)
@@ -7093,7 +7089,7 @@
 $45,823/呎</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>12号屋
 2716呎 (4+房)
@@ -7102,7 +7098,7 @@
 -</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>15号屋
 2695呎 (4+房)
@@ -7145,7 +7141,7 @@
 $65,801/呎</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>19号屋
 3059呎 (4+房)
@@ -7206,7 +7202,7 @@
 $49,504/呎</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>26号屋
 3350呎 (4+房)
@@ -7240,7 +7236,7 @@
           <t>第 5 行</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>29号屋
 3382呎 (4+房)
@@ -7267,7 +7263,7 @@
 $35,099/呎</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>32号屋
 3063呎 (4+房)
@@ -7301,7 +7297,7 @@
           <t>第 6 行</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>36号屋
 3063呎 (4+房)
@@ -7569,7 +7565,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7579,7 +7575,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7659,12 +7655,12 @@
 (24年-05月-10日)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 2436呎 (4+房)
-招标单位
--
-(在售)</t>
+$8468万
+$34,762/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -8260,7 +8256,7 @@
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1874呎 (4+房)
 -
@@ -8268,7 +8264,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 1855呎 (4+房)
 招标单位
@@ -8433,7 +8429,7 @@
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1931呎 (4+房)
 -
@@ -8441,7 +8437,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1910呎 (4+房)
 -
@@ -8456,7 +8452,7 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 844呎 (2房)
 招标单位
@@ -8613,7 +8609,7 @@
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 2403呎 (4+房)
 -

--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -172,7 +172,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -221,12 +221,6 @@
         <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -254,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -339,9 +333,6 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -708,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N84"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5447,7 +5438,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>23号屋</t>
+          <t>26号屋</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -5466,23 +5457,27 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>3272</v>
+        <v>3350</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="n">
-        <v>139988888</v>
-      </c>
-      <c r="I72" s="5" t="n">
-        <v>42784</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5513,7 +5508,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>25号屋</t>
+          <t>27号屋</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5532,7 +5527,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>3289</v>
+        <v>3304</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5541,14 +5536,14 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>162820000</v>
+        <v>146036800</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>49504</v>
+        <v>44200</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5579,7 +5574,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26号屋</t>
+          <t>28号屋</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -5598,27 +5593,23 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>3350</v>
+        <v>5260</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>260341664</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>49495</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5649,7 +5640,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>27号屋</t>
+          <t>29号屋</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5668,23 +5659,27 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>3304</v>
+        <v>3382</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>146036800</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>44200</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5693,12 +5688,12 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -5708,14 +5703,14 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>28号屋</t>
+          <t>30号屋</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5734,7 +5729,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>5260</v>
+        <v>2738</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5743,14 +5738,14 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>260341664</v>
+        <v>107460000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>49495</v>
+        <v>39248</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5781,7 +5776,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>29号屋</t>
+          <t>31号屋</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5800,27 +5795,23 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>3382</v>
+        <v>2739</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>96136000</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>35099</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5829,12 +5820,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -5844,14 +5835,14 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>30号屋</t>
+          <t>32号屋</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -5870,23 +5861,27 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2738</v>
+        <v>3063</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>107460000</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>39248</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5895,12 +5890,12 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -5910,14 +5905,14 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>31号屋</t>
+          <t>33号屋</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5936,7 +5931,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>2739</v>
+        <v>3102</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5945,14 +5940,14 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
-        <v>96136000</v>
+        <v>115238700</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>35099</v>
+        <v>37150</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5983,7 +5978,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>32号屋</t>
+          <t>35号屋</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -6002,27 +5997,23 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>3063</v>
+        <v>3102</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>115840200</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>37344</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -6031,12 +6022,12 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -6046,14 +6037,14 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>33号屋</t>
+          <t>36号屋</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -6072,23 +6063,27 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>3102</v>
+        <v>3063</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>115238700</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>37150</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6097,12 +6092,12 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -6112,14 +6107,14 @@
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>35号屋</t>
+          <t>38号屋</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -6138,7 +6133,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>3102</v>
+        <v>4692</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -6147,14 +6142,14 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
-        <v>115840200</v>
+        <v>256000000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>37344</v>
+        <v>54561</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6177,142 +6172,6 @@
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>36号屋</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="n">
-        <v>3063</v>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>在售</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>38号屋</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>4692</v>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>256000000</v>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>54561</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N84" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6866,7 +6725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6920,7 +6779,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>32 套</t>
+          <t>30 套</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -6935,7 +6794,7 @@
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
-          <t>20 套</t>
+          <t>18 套</t>
         </is>
       </c>
       <c r="E3" s="28" t="inlineStr">
@@ -7184,25 +7043,7 @@
 $42,009/呎</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>23号屋
-3272呎 (4+房)
-(25年-09月-04日)
-$1.40亿
-$42,784/呎</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>25号屋
-3289呎 (4+房)
-(26年-07月-27日)
-$1.63亿
-$49,504/呎</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>26号屋
 3350呎 (4+房)
@@ -7211,7 +7052,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>27号屋
 3304呎 (4+房)
@@ -7220,7 +7061,7 @@
 $44,200/呎</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>28号屋
 5260呎 (4+房)
@@ -7229,14 +7070,7 @@
 $49,495/呎</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>29号屋
 3382呎 (4+房)
@@ -7245,7 +7079,7 @@
 -</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>30号屋
 2738呎 (4+房)
@@ -7254,7 +7088,14 @@
 $39,248/呎</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>31号屋
 2739呎 (4+房)
@@ -7263,7 +7104,7 @@
 $35,099/呎</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>32号屋
 3063呎 (4+房)
@@ -7272,7 +7113,7 @@
 -</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>33号屋
 3102呎 (4+房)
@@ -7281,7 +7122,7 @@
 $37,150/呎</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>35号屋
 3102呎 (4+房)
@@ -7290,14 +7131,7 @@
 $37,344/呎</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>36号屋
 3063呎 (4+房)
@@ -7306,7 +7140,7 @@
 -</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>38号屋
 4692呎 (4+房)
@@ -7315,10 +7149,6 @@
 $54,561/呎</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr"/>
-      <c r="E11" s="29" t="inlineStr"/>
-      <c r="F11" s="29" t="inlineStr"/>
-      <c r="G11" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/web/files/港岛-赤柱-One Stanley.xlsx
+++ b/web/files/港岛-赤柱-One Stanley.xlsx
@@ -172,7 +172,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -221,6 +221,12 @@
         <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -248,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -333,6 +339,9 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -699,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -4114,7 +4123,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -5057,7 +5066,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>3059</v>
+        <v>3034</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -5066,14 +5075,14 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
         <v>118070000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>38598</v>
+        <v>38916</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -5438,7 +5447,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26号屋</t>
+          <t>23号屋</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -5457,27 +5466,23 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>3350</v>
+        <v>3272</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>139988888</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>42784</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5508,7 +5513,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>27号屋</t>
+          <t>25号屋</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5527,7 +5532,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>3304</v>
+        <v>3289</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5536,14 +5541,14 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>146036800</v>
+        <v>162820000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>44200</v>
+        <v>49504</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5574,7 +5579,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>28号屋</t>
+          <t>26号屋</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -5593,23 +5598,27 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>5260</v>
+        <v>3350</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>260341664</v>
-      </c>
-      <c r="I74" s="5" t="n">
-        <v>49495</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5640,7 +5649,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>29号屋</t>
+          <t>27号屋</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5659,27 +5668,23 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>3382</v>
+        <v>3304</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>146036800</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>44200</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5688,12 +5693,12 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -5703,14 +5708,14 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>30号屋</t>
+          <t>28号屋</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5729,7 +5734,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>2738</v>
+        <v>5260</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5738,14 +5743,14 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>107460000</v>
+        <v>260341664</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>39248</v>
+        <v>49495</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5776,7 +5781,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>31号屋</t>
+          <t>29号屋</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5795,23 +5800,27 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>2739</v>
+        <v>3382</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>96136000</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>35099</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5820,12 +5829,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -5835,14 +5844,14 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>32号屋</t>
+          <t>30号屋</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -5861,27 +5870,23 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>3063</v>
+        <v>2738</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>107460000</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>39248</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5890,12 +5895,12 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -5905,14 +5910,14 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>33号屋</t>
+          <t>31号屋</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5931,7 +5936,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>3102</v>
+        <v>2739</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5940,14 +5945,14 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
-        <v>115238700</v>
+        <v>96136000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>37150</v>
+        <v>35099</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5978,7 +5983,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>35号屋</t>
+          <t>32号屋</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -5997,23 +6002,27 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>3102</v>
+        <v>3063</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>115840200</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>37344</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -6022,12 +6031,12 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -6037,14 +6046,14 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>36号屋</t>
+          <t>33号屋</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -6063,27 +6072,23 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>3063</v>
+        <v>3102</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>115238700</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>37150</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6092,12 +6097,12 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -6107,71 +6112,207 @@
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
+          <t>35号屋</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>3102</v>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>115840200</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>37344</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>36号屋</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>3063</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
           <t>38号屋</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="E84" s="4" t="n">
         <v>4692</v>
       </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>已售</t>
         </is>
       </c>
-      <c r="G82" s="3" t="inlineStr">
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>2025-11-07</t>
         </is>
       </c>
-      <c r="H82" s="5" t="n">
+      <c r="H84" s="5" t="n">
         <v>256000000</v>
       </c>
-      <c r="I82" s="5" t="n">
+      <c r="I84" s="5" t="n">
         <v>54561</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" s="3" t="inlineStr">
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6696,7 +6837,7 @@
           <t>A | 2436呎 (4+房)
 $8695万
 $35,694/呎
-(26年-08月-12日)</t>
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -6725,7 +6866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6779,7 +6920,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>30 套</t>
+          <t>32 套</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -6794,7 +6935,7 @@
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
-          <t>18 套</t>
+          <t>20 套</t>
         </is>
       </c>
       <c r="E3" s="28" t="inlineStr">
@@ -6985,10 +7126,10 @@
       <c r="C8" s="21" t="inlineStr">
         <is>
           <t>17号屋
-3059呎 (4+房)
-(26年-08月-12日)
+3034呎 (4+房)
+(26年-09月-02日)
 $1.18亿
-$38,598/呎</t>
+$38,916/呎</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -7043,7 +7184,25 @@
 $42,009/呎</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>23号屋
+3272呎 (4+房)
+(25年-09月-04日)
+$1.40亿
+$42,784/呎</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>25号屋
+3289呎 (4+房)
+(26年-07月-27日)
+$1.63亿
+$49,504/呎</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>26号屋
 3350呎 (4+房)
@@ -7052,7 +7211,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>27号屋
 3304呎 (4+房)
@@ -7061,7 +7220,7 @@
 $44,200/呎</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>28号屋
 5260呎 (4+房)
@@ -7070,7 +7229,14 @@
 $49,495/呎</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>29号屋
 3382呎 (4+房)
@@ -7079,7 +7245,7 @@
 -</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>30号屋
 2738呎 (4+房)
@@ -7088,14 +7254,7 @@
 $39,248/呎</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>31号屋
 2739呎 (4+房)
@@ -7104,7 +7263,7 @@
 $35,099/呎</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>32号屋
 3063呎 (4+房)
@@ -7113,7 +7272,7 @@
 -</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>33号屋
 3102呎 (4+房)
@@ -7122,7 +7281,7 @@
 $37,150/呎</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>35号屋
 3102呎 (4+房)
@@ -7131,7 +7290,14 @@
 $37,344/呎</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>36号屋
 3063呎 (4+房)
@@ -7140,7 +7306,7 @@
 -</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>38号屋
 4692呎 (4+房)
@@ -7149,6 +7315,10 @@
 $54,561/呎</t>
         </is>
       </c>
+      <c r="D11" s="29" t="inlineStr"/>
+      <c r="E11" s="29" t="inlineStr"/>
+      <c r="F11" s="29" t="inlineStr"/>
+      <c r="G11" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
